--- a/cv_analyzer/data/jobs.xlsx
+++ b/cv_analyzer/data/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-925426C4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-05-14 14:48:06</t>
+          <t>2026-05-14 14:48:11</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -590,17 +590,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JOB-925426C4</t>
+          <t>JOB-CEC891D2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Hardware Engineer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -620,34 +620,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>We are looking for a creative and detail-oriented Software Designer to join our team. The Software Designer will be responsible for designing user-friendly software solutions, creating system layouts and interfaces, and working closely with developers, analysts, and stakeholders to ensure high-quality software products are delivered. The ideal candidate should have strong problem-solving skills, a passion for technology, and the ability to transform business requirements into effective software designs.</t>
+          <t>This is not a standard IT support role. You will train across two of our three service lines — IT Services and Electronic Security — which means that by the end of the programme you will be comfortable administering a Microsoft 365 tenant in the morning and commissioning an IP CCTV system in the afternoon. That kind of range is rare for a graduate in Zimbabwe, and it is what makes ZHD engineers genuinely employable.
+You will work alongside senior engineers on live client environments — not simulated lab exercises — and you will be expected to contribute meaningfully from month three onwards.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Design software systems, user interfaces, and application workflows.
-Create wireframes, mockups, prototypes, and technical design documents.
-Collaborate with developers, project managers, and clients to understand project requirements.
-Ensure software designs meet user experience (UX) and functionality standards.
-Conduct research on modern design trends and emerging technologies.
-Review and improve existing software systems and interfaces.
-Work closely with development teams during implementation and testing phases.
-Ensure consistency in branding, design standards, and usability across applications.
-Participate in software planning, brainstorming, and review meetings.
-Troubleshoot design-related issues and recommend improvements</t>
+          <t>•	Provide first-line technical support for hardware, software, printing and network issues.
+•	Install, configure and maintain Windows 10/11 systems, printers, routers, switches and Wi-Fi infrastructure.
+•	Administer Microsoft 365 — user setup, mailbox configuration, and troubleshooting.
+•	Assist with endpoint protection and firewall configurations (Sophos and similar platforms).
+•	Contribute to infrastructure deployments and upgrades.
+Electronic Security
+•	Support the installation, configuration and maintenance of IP CCTV, access control, and time &amp; attendance systems.
+•	Perform routine preventive maintenance on integrated IT and security equipment.
+•	Document system configurations, handovers and incident resolutions.
+Across Both Service Lines
+•	Deliver onsite and remote client support in line with agreed SLAs.
+•	Troubleshoot network connectivity and performance issues.
+•	Maintain accurate, client-ready records of support cases and system changes.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Diploma or Degree in Computer Science, Software Engineering, Information Technology, Graphic Design, or a related field.
-Experience in software design, UI/UX design, or application development.
-Knowledge of design tools such as Figma, Adobe XD, Sketch, or similar platforms.
-Understanding of front-end technologies such as HTML, CSS, JavaScript, and responsive design principles.
-Familiarity with software development processes and agile methodologies.
-Strong creativity, analytical thinking, and problem-solving abilities.
-Excellent communication and teamwork skills.
-Ability to manage multiple projects and meet deadlines.
-Portfolio of previous software or UI/UX design projects is an added advantage.</t>
+          <t>•	Recently completed a Degree or Diploma in Information Technology, Computer Science, or a related field.
+•	Working understanding of computer hardware and operating systems.
+•	Familiarity with Microsoft Windows and Microsoft Office environments.
+•	Grounding in networking fundamentals (TCP/IP, DNS, DHCP).
+•	Strong problem-solving and analytical ability.
+•	Clear written and verbal communication.
+•	Capable of working independently and within a team.
+ADDED ADVANTAGE
+•	CompTIA A+, Network+, or equivalent certifications.
+•	Microsoft certifications (Fundamentals or Associate level).
+•	Prior exposure to CCTV, access control, or cybersecurity tooling.
+•	Familiarity with Linux or Windows Server environments.
+•	A valid driver's licence.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -657,12 +665,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-05-14 14:48:11</t>
+          <t>2026-05-19 11:29:14</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -671,6 +679,93 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JOB-492B2F1A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>We are seeking a skilled and proactive Network Engineer to join our team. The Network Engineer will be responsible for designing, implementing, maintaining, and troubleshooting the organization’s network infrastructure to ensure reliable and secure communication systems. The ideal candidate should have strong technical knowledge of networking technologies, excellent problem-solving skills, and the ability to work in a fast-paced environment.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Design, install, configure, and maintain network infrastructure including routers, switches, firewalls, and wireless networks.
+Monitor network performance and ensure system availability and reliability.
+Troubleshoot network issues and provide timely resolutions.
+Implement network security measures to protect systems and data.
+Configure and manage LAN, WAN, VPN, and wireless network connections.
+Perform regular network maintenance, upgrades, and backups.
+Collaborate with IT teams and other departments to support business operations.
+Maintain accurate documentation of network configurations and procedures.
+Ensure compliance with network policies, standards, and best practices.
+Provide technical support and guidance to users when required.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Diploma or Degree in Computer Science, Information Technology, Network Engineering, or a related field.
+Proven experience in network administration or network engineering.
+Strong understanding of networking concepts such as TCP/IP, DNS, DHCP, VLANs, and routing protocols.
+Experience with networking hardware and software from vendors such as Cisco, Mikrotik, HP, or Juniper.
+Knowledge of network security practices, firewalls, and VPN technologies.
+Familiarity with monitoring and troubleshooting tools.
+Excellent analytical, troubleshooting, and problem-solving skills.
+Strong communication and teamwork abilities.
+Ability to work independently and manage multiple tasks effectively.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:32:33</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/cv_analyzer/data/jobs.xlsx
+++ b/cv_analyzer/data/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JOB-925426C4</t>
+          <t>JOB-FAE79E5C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GRADUATE TRAINEE IT &amp; Electronic Security Support Engineer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,101 +532,15 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>We are looking for a creative and detail-oriented Software Designer to join our team. The Software Designer will be responsible for designing user-friendly software solutions, creating system layouts and interfaces, and working closely with developers, analysts, and stakeholders to ensure high-quality software products are delivered. The ideal candidate should have strong problem-solving skills, a passion for technology, and the ability to transform business requirements into effective software designs.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Design software systems, user interfaces, and application workflows.
-Create wireframes, mockups, prototypes, and technical design documents.
-Collaborate with developers, project managers, and clients to understand project requirements.
-Ensure software designs meet user experience (UX) and functionality standards.
-Conduct research on modern design trends and emerging technologies.
-Review and improve existing software systems and interfaces.
-Work closely with development teams during implementation and testing phases.
-Ensure consistency in branding, design standards, and usability across applications.
-Participate in software planning, brainstorming, and review meetings.
-Troubleshoot design-related issues and recommend improvements</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Diploma or Degree in Computer Science, Software Engineering, Information Technology, Graphic Design, or a related field.
-Experience in software design, UI/UX design, or application development.
-Knowledge of design tools such as Figma, Adobe XD, Sketch, or similar platforms.
-Understanding of front-end technologies such as HTML, CSS, JavaScript, and responsive design principles.
-Familiarity with software development processes and agile methodologies.
-Strong creativity, analytical thinking, and problem-solving abilities.
-Excellent communication and teamwork skills.
-Ability to manage multiple projects and meet deadlines.
-Portfolio of previous software or UI/UX design projects is an added advantage.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-05-14 14:48:11</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>JOB-CEC891D2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Hardware Engineer</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>On-site</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Harare</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t>This is not a standard IT support role. You will train across two of our three service lines — IT Services and Electronic Security — which means that by the end of the programme you will be comfortable administering a Microsoft 365 tenant in the morning and commissioning an IP CCTV system in the afternoon. That kind of range is rare for a graduate in Zimbabwe, and it is what makes ZHD engineers genuinely employable.
 You will work alongside senior engineers on live client environments — not simulated lab exercises — and you will be expected to contribute meaningfully from month three onwards.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>•	Provide first-line technical support for hardware, software, printing and network issues.
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IT Services
+•	Provide first-line technical support for hardware, software, printing and network issues.
 •	Install, configure and maintain Windows 10/11 systems, printers, routers, switches and Wi-Fi infrastructure.
 •	Administer Microsoft 365 — user setup, mailbox configuration, and troubleshooting.
 •	Assist with endpoint protection and firewall configurations (Sophos and similar platforms).
@@ -641,7 +555,7 @@
 •	Maintain accurate, client-ready records of support cases and system changes.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>•	Recently completed a Degree or Diploma in Information Technology, Computer Science, or a related field.
 •	Working understanding of computer hardware and operating systems.
@@ -649,124 +563,31 @@
 •	Grounding in networking fundamentals (TCP/IP, DNS, DHCP).
 •	Strong problem-solving and analytical ability.
 •	Clear written and verbal communication.
-•	Capable of working independently and within a team.
-ADDED ADVANTAGE
-•	CompTIA A+, Network+, or equivalent certifications.
-•	Microsoft certifications (Fundamentals or Associate level).
-•	Prior exposure to CCTV, access control, or cybersecurity tooling.
-•	Familiarity with Linux or Windows Server environments.
-•	A valid driver's licence.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+•	Capable of working independently and within a team.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-05-19 11:29:14</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>JOB-492B2F1A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Network Engineer</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>On-site</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Harare</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>We are seeking a skilled and proactive Network Engineer to join our team. The Network Engineer will be responsible for designing, implementing, maintaining, and troubleshooting the organization’s network infrastructure to ensure reliable and secure communication systems. The ideal candidate should have strong technical knowledge of networking technologies, excellent problem-solving skills, and the ability to work in a fast-paced environment.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Design, install, configure, and maintain network infrastructure including routers, switches, firewalls, and wireless networks.
-Monitor network performance and ensure system availability and reliability.
-Troubleshoot network issues and provide timely resolutions.
-Implement network security measures to protect systems and data.
-Configure and manage LAN, WAN, VPN, and wireless network connections.
-Perform regular network maintenance, upgrades, and backups.
-Collaborate with IT teams and other departments to support business operations.
-Maintain accurate documentation of network configurations and procedures.
-Ensure compliance with network policies, standards, and best practices.
-Provide technical support and guidance to users when required.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Diploma or Degree in Computer Science, Information Technology, Network Engineering, or a related field.
-Proven experience in network administration or network engineering.
-Strong understanding of networking concepts such as TCP/IP, DNS, DHCP, VLANs, and routing protocols.
-Experience with networking hardware and software from vendors such as Cisco, Mikrotik, HP, or Juniper.
-Knowledge of network security practices, firewalls, and VPN technologies.
-Familiarity with monitoring and troubleshooting tools.
-Excellent analytical, troubleshooting, and problem-solving skills.
-Strong communication and teamwork abilities.
-Ability to work independently and manage multiple tasks effectively.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-05-19 14:32:33</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:23:56</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/cv_analyzer/data/jobs.xlsx
+++ b/cv_analyzer/data/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,96 +498,6 @@
         <is>
           <t>Is Active</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>JOB-FAE79E5C</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GRADUATE TRAINEE IT &amp; Electronic Security Support Engineer</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>On-site</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Harare</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>This is not a standard IT support role. You will train across two of our three service lines — IT Services and Electronic Security — which means that by the end of the programme you will be comfortable administering a Microsoft 365 tenant in the morning and commissioning an IP CCTV system in the afternoon. That kind of range is rare for a graduate in Zimbabwe, and it is what makes ZHD engineers genuinely employable.
-You will work alongside senior engineers on live client environments — not simulated lab exercises — and you will be expected to contribute meaningfully from month three onwards.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>IT Services
-•	Provide first-line technical support for hardware, software, printing and network issues.
-•	Install, configure and maintain Windows 10/11 systems, printers, routers, switches and Wi-Fi infrastructure.
-•	Administer Microsoft 365 — user setup, mailbox configuration, and troubleshooting.
-•	Assist with endpoint protection and firewall configurations (Sophos and similar platforms).
-•	Contribute to infrastructure deployments and upgrades.
-Electronic Security
-•	Support the installation, configuration and maintenance of IP CCTV, access control, and time &amp; attendance systems.
-•	Perform routine preventive maintenance on integrated IT and security equipment.
-•	Document system configurations, handovers and incident resolutions.
-Across Both Service Lines
-•	Deliver onsite and remote client support in line with agreed SLAs.
-•	Troubleshoot network connectivity and performance issues.
-•	Maintain accurate, client-ready records of support cases and system changes.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>•	Recently completed a Degree or Diploma in Information Technology, Computer Science, or a related field.
-•	Working understanding of computer hardware and operating systems.
-•	Familiarity with Microsoft Windows and Microsoft Office environments.
-•	Grounding in networking fundamentals (TCP/IP, DNS, DHCP).
-•	Strong problem-solving and analytical ability.
-•	Clear written and verbal communication.
-•	Capable of working independently and within a team.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-05-20 15:23:56</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/cv_analyzer/data/jobs.xlsx
+++ b/cv_analyzer/data/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,102 @@
         <is>
           <t>Is Active</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JOB-4D77368B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GRADUATE TRAINEE IT &amp; Electronic Security Support Engineer</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>This is not a standard IT support role. You will train across two of our three service lines — IT Services and Electronic Security — which means that by the end of the programme you will be comfortable administering a Microsoft 365 tenant in the morning and commissioning an IP CCTV system in the afternoon. That kind of range is rare for a graduate in Zimbabwe, and it is what makes ZHD engineers genuinely employable.
+You will work alongside senior engineers on live client environments — not simulated lab exercises — and you will be expected to contribute meaningfully from month three onwards.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IT Services
+•	Provide first-line technical support for hardware, software, printing and network issues.
+•	Install, configure and maintain Windows 10/11 systems, printers, routers, switches and Wi-Fi infrastructure.
+•	Administer Microsoft 365 — user setup, mailbox configuration, and troubleshooting.
+•	Assist with endpoint protection and firewall configurations (Sophos and similar platforms).
+•	Contribute to infrastructure deployments and upgrades.
+Electronic Security
+•	Support the installation, configuration and maintenance of IP CCTV, access control, and time &amp; attendance systems.
+•	Perform routine preventive maintenance on integrated IT and security equipment.
+•	Document system configurations, handovers and incident resolutions.
+Across Both Service Lines
+•	Deliver onsite and remote client support in line with agreed SLAs.
+•	Troubleshoot network connectivity and performance issues.
+•	Maintain accurate, client-ready records of support cases and system changes.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>•	Recently completed a Degree or Diploma in Information Technology, Computer Science, or a related field.
+•	Working understanding of computer hardware and operating systems.
+•	Familiarity with Microsoft Windows and Microsoft Office environments.
+•	Grounding in networking fundamentals (TCP/IP, DNS, DHCP).
+•	Strong problem-solving and analytical ability.
+•	Clear written and verbal communication.
+•	Capable of working independently and within a team.
+ADDED ADVANTAGE
+•	CompTIA A+, Network+, or equivalent certifications.
+•	Microsoft certifications (Fundamentals or Associate level).
+•	Prior exposure to CCTV, access control, or cybersecurity tooling.
+•	Familiarity with Linux or Windows Server environments.
+•	A valid driver's licence.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:20:09</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/cv_analyzer/data/jobs.xlsx
+++ b/cv_analyzer/data/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,102 +498,6 @@
         <is>
           <t>Is Active</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>JOB-4D77368B</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GRADUATE TRAINEE IT &amp; Electronic Security Support Engineer</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>On-site</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Harare</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>This is not a standard IT support role. You will train across two of our three service lines — IT Services and Electronic Security — which means that by the end of the programme you will be comfortable administering a Microsoft 365 tenant in the morning and commissioning an IP CCTV system in the afternoon. That kind of range is rare for a graduate in Zimbabwe, and it is what makes ZHD engineers genuinely employable.
-You will work alongside senior engineers on live client environments — not simulated lab exercises — and you will be expected to contribute meaningfully from month three onwards.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>IT Services
-•	Provide first-line technical support for hardware, software, printing and network issues.
-•	Install, configure and maintain Windows 10/11 systems, printers, routers, switches and Wi-Fi infrastructure.
-•	Administer Microsoft 365 — user setup, mailbox configuration, and troubleshooting.
-•	Assist with endpoint protection and firewall configurations (Sophos and similar platforms).
-•	Contribute to infrastructure deployments and upgrades.
-Electronic Security
-•	Support the installation, configuration and maintenance of IP CCTV, access control, and time &amp; attendance systems.
-•	Perform routine preventive maintenance on integrated IT and security equipment.
-•	Document system configurations, handovers and incident resolutions.
-Across Both Service Lines
-•	Deliver onsite and remote client support in line with agreed SLAs.
-•	Troubleshoot network connectivity and performance issues.
-•	Maintain accurate, client-ready records of support cases and system changes.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>•	Recently completed a Degree or Diploma in Information Technology, Computer Science, or a related field.
-•	Working understanding of computer hardware and operating systems.
-•	Familiarity with Microsoft Windows and Microsoft Office environments.
-•	Grounding in networking fundamentals (TCP/IP, DNS, DHCP).
-•	Strong problem-solving and analytical ability.
-•	Clear written and verbal communication.
-•	Capable of working independently and within a team.
-ADDED ADVANTAGE
-•	CompTIA A+, Network+, or equivalent certifications.
-•	Microsoft certifications (Fundamentals or Associate level).
-•	Prior exposure to CCTV, access control, or cybersecurity tooling.
-•	Familiarity with Linux or Windows Server environments.
-•	A valid driver's licence.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-05-20 17:20:09</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/cv_analyzer/data/jobs.xlsx
+++ b/cv_analyzer/data/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,103 @@
         <is>
           <t>Is Active</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JOB-9263A2FF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GRADUATE TRAINEE IT &amp; Electronic Security Support Engineer</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>This is not a standard IT support role. You will train across two of our three service lines — IT Services and Electronic Security — which means that by the end of the programme you will be comfortable administering a Microsoft 365 tenant in the morning and commissioning an IP CCTV system in the afternoon. That kind of range is rare for a graduate in Zimbabwe, and it is what makes ZHD engineers genuinely employable.
+You will work alongside senior engineers on live client environments — not simulated lab exercises — and you will be expected to contribute meaningfully from month three onwards.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IT Services
+•	Provide first-line technical support for hardware, software, printing and network issues.
+•	Install, configure and maintain Windows 10/11 systems, printers, routers, switches and Wi-Fi infrastructure.
+•	Administer Microsoft 365 — user setup, mailbox configuration, and troubleshooting.
+•	Assist with endpoint protection and firewall configurations (Sophos and similar platforms).
+•	Contribute to infrastructure deployments and upgrades.
+Electronic Security
+•	Support the installation, configuration and maintenance of IP CCTV, access control, and time &amp; attendance systems.
+•	Perform routine preventive maintenance on integrated IT and security equipment.
+•	Document system configurations, handovers and incident resolutions.
+Across Both Service Lines
+•	Deliver onsite and remote client support in line with agreed SLAs.
+•	Troubleshoot network connectivity and performance issues.
+•	Maintain accurate, client-ready records of support cases and system changes.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MINIMUM REQUIREMENTS
+•	Recently completed a Degree or Diploma in Information Technology, Computer Science, or a related field.
+•	Working understanding of computer hardware and operating systems.
+•	Familiarity with Microsoft Windows and Microsoft Office environments.
+•	Grounding in networking fundamentals (TCP/IP, DNS, DHCP).
+•	Strong problem-solving and analytical ability.
+•	Clear written and verbal communication.
+•	Capable of working independently and within a team.
+ADDED ADVANTAGE
+•	CompTIA A+, Network+, or equivalent certifications.
+•	Microsoft certifications (Fundamentals or Associate level).
+•	Prior exposure to CCTV, access control, or cybersecurity tooling.
+•	Familiarity with Linux or Windows Server environments.
+•	A valid driver's licence.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-05-26 07:33:43</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
